--- a/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
+++ b/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
   <si>
     <t>Type</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>Begriff - Änderungsvermerk (de)</t>
+  </si>
+  <si>
+    <t>https://www.wikidata.org/w/index.php?title=Q97379970&amp;oldid=1936875884</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +1715,9 @@
         <v>72</v>
       </c>
       <c r="J13" s="10"/>
-      <c r="K13" s="21"/>
+      <c r="K13" s="21" t="s">
+        <v>79</v>
+      </c>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>

--- a/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
+++ b/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
   <si>
     <t>Type</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>https://www.wikidata.org/w/index.php?title=Q97379970&amp;oldid=1936875884</t>
+  </si>
+  <si>
+    <t>Begriff - ist Top Concept</t>
   </si>
 </sst>
 </file>
@@ -374,12 +377,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -392,9 +410,7 @@
       <top style="thin">
         <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -407,9 +423,7 @@
       <top style="thin">
         <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -422,343 +436,822 @@
       <top style="thin">
         <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF284E3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF284E3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF6F8F9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF6F8F9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF6F8F9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF6F8F9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF6F8F9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF6F8F9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF6F8F9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF6F8F9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF6F8F9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF6F8F9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF284E3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF6F8F9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF6F8F9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF6F8F9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF6F8F9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF6F8F9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="37">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -800,9 +1293,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Tabellenblatt1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="36"/>
+      <tableStyleElement type="firstRowStripe" dxfId="35"/>
+      <tableStyleElement type="secondRowStripe" dxfId="34"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -817,40 +1310,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AF14" headerRowDxfId="0">
-  <tableColumns count="32">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Verfasser - ID"/>
-    <tableColumn id="3" name="Verfasser  - Nachname"/>
-    <tableColumn id="4" name="Verfasser - Vorname"/>
-    <tableColumn id="5" name="Verfasser - ORCiD"/>
-    <tableColumn id="6" name="Quellennachweis - ID"/>
-    <tableColumn id="7" name="Quellennachweis - Titel"/>
-    <tableColumn id="8" name="Quellennachweis - Verfasser"/>
-    <tableColumn id="9" name="Quellennachweis - Herausgeber"/>
-    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum"/>
-    <tableColumn id="11" name="Quellennachweis - Zugangslink"/>
-    <tableColumn id="12" name="Begriff - ID"/>
-    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)"/>
-    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)"/>
-    <tableColumn id="15" name="Begriff - alternative Benennung (de)"/>
-    <tableColumn id="16" name="Begriff - alternative Benennung (en)"/>
-    <tableColumn id="17" name="Begriff - Definition (de)"/>
-    <tableColumn id="18" name="Begriff - Definition (en)"/>
-    <tableColumn id="19" name="Begriff - Quellenangabe"/>
-    <tableColumn id="20" name="Begriff - Bearbeitungsdatum"/>
-    <tableColumn id="21" name="Begriff - Fachzuordnung"/>
-    <tableColumn id="22" name="Begriff - Erstellungsdatum"/>
-    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)"/>
-    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)"/>
-    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)"/>
-    <tableColumn id="26" name="Begriff - Änderungsvermerk (en)"/>
-    <tableColumn id="27" name="Begriff - Verfasser des Eintrags"/>
-    <tableColumn id="28" name="Begriff - Kontextsatz (de)"/>
-    <tableColumn id="29" name="Begriff - Kontextsatz (en)"/>
-    <tableColumn id="30" name="Begriff - Bearbeitungsstatus"/>
-    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen"/>
-    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AG14" headerRowDxfId="33">
+  <tableColumns count="33">
+    <tableColumn id="1" name="Type" dataDxfId="32"/>
+    <tableColumn id="2" name="Verfasser - ID" dataDxfId="31"/>
+    <tableColumn id="3" name="Verfasser  - Nachname" dataDxfId="30"/>
+    <tableColumn id="4" name="Verfasser - Vorname" dataDxfId="29"/>
+    <tableColumn id="5" name="Verfasser - ORCiD" dataDxfId="28"/>
+    <tableColumn id="6" name="Quellennachweis - ID" dataDxfId="27"/>
+    <tableColumn id="7" name="Quellennachweis - Titel" dataDxfId="26"/>
+    <tableColumn id="8" name="Quellennachweis - Verfasser" dataDxfId="25"/>
+    <tableColumn id="9" name="Quellennachweis - Herausgeber" dataDxfId="24"/>
+    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum" dataDxfId="23"/>
+    <tableColumn id="11" name="Quellennachweis - Zugangslink" dataDxfId="22"/>
+    <tableColumn id="12" name="Begriff - ID" dataDxfId="21"/>
+    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)" dataDxfId="20"/>
+    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)" dataDxfId="19"/>
+    <tableColumn id="15" name="Begriff - alternative Benennung (de)" dataDxfId="18"/>
+    <tableColumn id="16" name="Begriff - alternative Benennung (en)" dataDxfId="17"/>
+    <tableColumn id="17" name="Begriff - Definition (de)" dataDxfId="16"/>
+    <tableColumn id="18" name="Begriff - Definition (en)" dataDxfId="15"/>
+    <tableColumn id="19" name="Begriff - Quellenangabe" dataDxfId="14"/>
+    <tableColumn id="20" name="Begriff - Bearbeitungsdatum" dataDxfId="13"/>
+    <tableColumn id="21" name="Begriff - Fachzuordnung" dataDxfId="12"/>
+    <tableColumn id="22" name="Begriff - Erstellungsdatum" dataDxfId="11"/>
+    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)" dataDxfId="10"/>
+    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)" dataDxfId="9"/>
+    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)" dataDxfId="8"/>
+    <tableColumn id="26" name="Begriff - Änderungsvermerk (en)" dataDxfId="7"/>
+    <tableColumn id="27" name="Begriff - Verfasser des Eintrags" dataDxfId="6"/>
+    <tableColumn id="28" name="Begriff - Kontextsatz (de)" dataDxfId="5"/>
+    <tableColumn id="29" name="Begriff - Kontextsatz (en)" dataDxfId="4"/>
+    <tableColumn id="30" name="Begriff - Bearbeitungsstatus" dataDxfId="3"/>
+    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen" dataDxfId="2"/>
+    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff" dataDxfId="1"/>
+    <tableColumn id="33" name="Begriff - ist Top Concept" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Tabellenblatt1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1057,7 +1551,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AF14"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
@@ -1082,709 +1576,725 @@
     <col min="25" max="25" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:33">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="55" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="55" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="55" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="55" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="55" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="56" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="55" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="55" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="55" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="55" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="55" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="55" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="55" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="55" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="55" t="s">
+      <c r="Y1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Z1" s="55" t="s">
+      <c r="Z1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AA1" s="55" t="s">
+      <c r="AA1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="55" t="s">
+      <c r="AB1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="55" t="s">
+      <c r="AC1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="55" t="s">
+      <c r="AD1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="55" t="s">
+      <c r="AE1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AF1" s="57" t="s">
+      <c r="AF1" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="AG1" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="2" spans="1:32">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:33">
+      <c r="A2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="7"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="10"/>
     </row>
-    <row r="3" spans="1:32">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:33">
+      <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="6">
         <v>2026</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13"/>
-      <c r="AF3" s="15"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="10"/>
     </row>
-    <row r="4" spans="1:32">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:33">
+      <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="11"/>
+      <c r="H4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="20"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="10"/>
     </row>
-    <row r="5" spans="1:32">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:33">
+      <c r="A5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="10" t="s">
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="10" t="s">
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="R5" s="10" t="s">
+      <c r="R5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S5" s="22" t="s">
+      <c r="S5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="T5" s="23">
+      <c r="T5" s="9">
         <v>45969</v>
       </c>
-      <c r="U5" s="24" t="s">
+      <c r="U5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="V5" s="23">
+      <c r="V5" s="9">
         <v>45811</v>
       </c>
-      <c r="W5" s="10" t="s">
+      <c r="W5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="X5" s="10" t="s">
+      <c r="X5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Y5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="Z5" s="10" t="s">
+      <c r="Z5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AA5" s="10" t="s">
+      <c r="AA5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AB5" s="10" t="s">
+      <c r="AB5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AC5" s="10" t="s">
+      <c r="AC5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AD5" s="10" t="s">
+      <c r="AD5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="25" t="s">
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6" t="s">
         <v>55</v>
       </c>
+      <c r="AG5" s="10"/>
     </row>
-    <row r="6" spans="1:32">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:33">
+      <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="3" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3" t="s">
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="3" t="s">
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5"/>
-      <c r="AF6" s="7"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
+      <c r="AG6" s="10"/>
     </row>
-    <row r="7" spans="1:32">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:33">
+      <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="10" t="s">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10" t="s">
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="15"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="10"/>
     </row>
-    <row r="8" spans="1:32">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:33">
+      <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="3" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="19">
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="9">
         <v>45969</v>
       </c>
-      <c r="U8" s="26" t="s">
+      <c r="U8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="V8" s="19">
+      <c r="V8" s="9">
         <v>45811</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="W8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="X8" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="3" t="s">
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="3" t="s">
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AE8" s="5"/>
-      <c r="AF8" s="7"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
+      <c r="AG8" s="10"/>
     </row>
-    <row r="9" spans="1:32">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:33">
+      <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="10" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="10" t="s">
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="X9" s="10" t="s">
+      <c r="X9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="15"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6"/>
+      <c r="AG9" s="10"/>
     </row>
-    <row r="10" spans="1:32">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:33">
+      <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="3" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="3" t="s">
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="X10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="7"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="10"/>
     </row>
-    <row r="11" spans="1:32">
-      <c r="A11" s="27" t="s">
+    <row r="11" spans="1:33">
+      <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="11"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="15"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="10"/>
     </row>
-    <row r="12" spans="1:32">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:33">
+      <c r="A12" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="7"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="10"/>
     </row>
-    <row r="13" spans="1:32">
-      <c r="A13" s="35" t="s">
+    <row r="13" spans="1:33">
+      <c r="A13" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="33" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="33" t="s">
+      <c r="H13" s="22"/>
+      <c r="I13" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="21" t="s">
+      <c r="J13" s="6"/>
+      <c r="K13" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="13"/>
-      <c r="AF13" s="15"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="10"/>
     </row>
-    <row r="14" spans="1:32">
-      <c r="A14" s="40" t="s">
+    <row r="14" spans="1:33">
+      <c r="A14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="47" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="M14" s="47" t="s">
+      <c r="M14" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="N14" s="48"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="49"/>
-      <c r="S14" s="50" t="s">
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="T14" s="51"/>
-      <c r="U14" s="52" t="s">
+      <c r="T14" s="25"/>
+      <c r="U14" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="V14" s="51"/>
-      <c r="W14" s="48"/>
-      <c r="X14" s="48"/>
-      <c r="Y14" s="49"/>
-      <c r="Z14" s="49"/>
-      <c r="AA14" s="47" t="s">
+      <c r="V14" s="25"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="AB14" s="49"/>
-      <c r="AC14" s="49"/>
-      <c r="AD14" s="49"/>
-      <c r="AE14" s="49"/>
-      <c r="AF14" s="53"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
+++ b/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
   <si>
     <t>Type</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Begriff - ist Top Concept</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
@@ -2026,7 +2029,9 @@
       </c>
       <c r="AE8" s="6"/>
       <c r="AF8" s="6"/>
-      <c r="AG8" s="10"/>
+      <c r="AG8" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="9" spans="1:33">
       <c r="A9" s="6" t="s">
@@ -2294,7 +2299,9 @@
       <c r="AD14" s="24"/>
       <c r="AE14" s="24"/>
       <c r="AF14" s="24"/>
-      <c r="AG14" s="10"/>
+      <c r="AG14" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
+++ b/OpenRefine_Templates/OpenRefineTemplate_wExampleData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="89">
   <si>
     <t>Type</t>
   </si>
@@ -265,6 +265,27 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>Begriff - ist veraltet?</t>
+  </si>
+  <si>
+    <t>Begriff - hat Nachfolger</t>
+  </si>
+  <si>
+    <t>Begriff - Grund der Markierung als veraltet (de)</t>
+  </si>
+  <si>
+    <t>Begriff - Grund der Markierung als veraltet (en)</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>Das Konzept des Parksuchverkehrs hat sich mit der Einführung von Park+Ride-Systemen, dem Ausbau des ÖPNV und intelligenten Parksuchassistenten quasi erledigt.</t>
+  </si>
+  <si>
+    <t>With the introduction of Park+Ride systems, the expansion of public transport and intelligent parking search assistants, the concept of searching for a parking space has virtually disappeared.</t>
   </si>
 </sst>
 </file>
@@ -380,7 +401,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -442,11 +463,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -524,11 +558,101 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="41">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1296,9 +1420,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Tabellenblatt1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="36"/>
-      <tableStyleElement type="firstRowStripe" dxfId="35"/>
-      <tableStyleElement type="secondRowStripe" dxfId="34"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="firstRowStripe" dxfId="39"/>
+      <tableStyleElement type="secondRowStripe" dxfId="38"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1313,41 +1437,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AG14" headerRowDxfId="33">
-  <tableColumns count="33">
-    <tableColumn id="1" name="Type" dataDxfId="32"/>
-    <tableColumn id="2" name="Verfasser - ID" dataDxfId="31"/>
-    <tableColumn id="3" name="Verfasser  - Nachname" dataDxfId="30"/>
-    <tableColumn id="4" name="Verfasser - Vorname" dataDxfId="29"/>
-    <tableColumn id="5" name="Verfasser - ORCiD" dataDxfId="28"/>
-    <tableColumn id="6" name="Quellennachweis - ID" dataDxfId="27"/>
-    <tableColumn id="7" name="Quellennachweis - Titel" dataDxfId="26"/>
-    <tableColumn id="8" name="Quellennachweis - Verfasser" dataDxfId="25"/>
-    <tableColumn id="9" name="Quellennachweis - Herausgeber" dataDxfId="24"/>
-    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum" dataDxfId="23"/>
-    <tableColumn id="11" name="Quellennachweis - Zugangslink" dataDxfId="22"/>
-    <tableColumn id="12" name="Begriff - ID" dataDxfId="21"/>
-    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)" dataDxfId="20"/>
-    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)" dataDxfId="19"/>
-    <tableColumn id="15" name="Begriff - alternative Benennung (de)" dataDxfId="18"/>
-    <tableColumn id="16" name="Begriff - alternative Benennung (en)" dataDxfId="17"/>
-    <tableColumn id="17" name="Begriff - Definition (de)" dataDxfId="16"/>
-    <tableColumn id="18" name="Begriff - Definition (en)" dataDxfId="15"/>
-    <tableColumn id="19" name="Begriff - Quellenangabe" dataDxfId="14"/>
-    <tableColumn id="20" name="Begriff - Bearbeitungsdatum" dataDxfId="13"/>
-    <tableColumn id="21" name="Begriff - Fachzuordnung" dataDxfId="12"/>
-    <tableColumn id="22" name="Begriff - Erstellungsdatum" dataDxfId="11"/>
-    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)" dataDxfId="10"/>
-    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)" dataDxfId="9"/>
-    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)" dataDxfId="8"/>
-    <tableColumn id="26" name="Begriff - Änderungsvermerk (en)" dataDxfId="7"/>
-    <tableColumn id="27" name="Begriff - Verfasser des Eintrags" dataDxfId="6"/>
-    <tableColumn id="28" name="Begriff - Kontextsatz (de)" dataDxfId="5"/>
-    <tableColumn id="29" name="Begriff - Kontextsatz (en)" dataDxfId="4"/>
-    <tableColumn id="30" name="Begriff - Bearbeitungsstatus" dataDxfId="3"/>
-    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen" dataDxfId="2"/>
-    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff" dataDxfId="1"/>
-    <tableColumn id="33" name="Begriff - ist Top Concept" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AK14" headerRowDxfId="37">
+  <tableColumns count="37">
+    <tableColumn id="1" name="Type" dataDxfId="36"/>
+    <tableColumn id="2" name="Verfasser - ID" dataDxfId="35"/>
+    <tableColumn id="3" name="Verfasser  - Nachname" dataDxfId="34"/>
+    <tableColumn id="4" name="Verfasser - Vorname" dataDxfId="33"/>
+    <tableColumn id="5" name="Verfasser - ORCiD" dataDxfId="32"/>
+    <tableColumn id="6" name="Quellennachweis - ID" dataDxfId="31"/>
+    <tableColumn id="7" name="Quellennachweis - Titel" dataDxfId="30"/>
+    <tableColumn id="8" name="Quellennachweis - Verfasser" dataDxfId="29"/>
+    <tableColumn id="9" name="Quellennachweis - Herausgeber" dataDxfId="28"/>
+    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum" dataDxfId="27"/>
+    <tableColumn id="11" name="Quellennachweis - Zugangslink" dataDxfId="26"/>
+    <tableColumn id="12" name="Begriff - ID" dataDxfId="25"/>
+    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)" dataDxfId="24"/>
+    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)" dataDxfId="23"/>
+    <tableColumn id="15" name="Begriff - alternative Benennung (de)" dataDxfId="22"/>
+    <tableColumn id="16" name="Begriff - alternative Benennung (en)" dataDxfId="21"/>
+    <tableColumn id="17" name="Begriff - Definition (de)" dataDxfId="20"/>
+    <tableColumn id="18" name="Begriff - Definition (en)" dataDxfId="19"/>
+    <tableColumn id="19" name="Begriff - Quellenangabe" dataDxfId="18"/>
+    <tableColumn id="20" name="Begriff - Bearbeitungsdatum" dataDxfId="17"/>
+    <tableColumn id="21" name="Begriff - Fachzuordnung" dataDxfId="16"/>
+    <tableColumn id="22" name="Begriff - Erstellungsdatum" dataDxfId="15"/>
+    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)" dataDxfId="14"/>
+    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)" dataDxfId="13"/>
+    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)" dataDxfId="12"/>
+    <tableColumn id="26" name="Begriff - Änderungsvermerk (en)" dataDxfId="11"/>
+    <tableColumn id="27" name="Begriff - Verfasser des Eintrags" dataDxfId="10"/>
+    <tableColumn id="28" name="Begriff - Kontextsatz (de)" dataDxfId="9"/>
+    <tableColumn id="29" name="Begriff - Kontextsatz (en)" dataDxfId="8"/>
+    <tableColumn id="30" name="Begriff - Bearbeitungsstatus" dataDxfId="7"/>
+    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen" dataDxfId="6"/>
+    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff" dataDxfId="5"/>
+    <tableColumn id="33" name="Begriff - ist Top Concept" dataDxfId="4"/>
+    <tableColumn id="34" name="Begriff - ist veraltet?" dataDxfId="3"/>
+    <tableColumn id="35" name="Begriff - hat Nachfolger" dataDxfId="2"/>
+    <tableColumn id="36" name="Begriff - Grund der Markierung als veraltet (de)" dataDxfId="1"/>
+    <tableColumn id="37" name="Begriff - Grund der Markierung als veraltet (en)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Tabellenblatt1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1554,7 +1682,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
@@ -1579,7 +1707,7 @@
     <col min="25" max="25" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:37" ht="12.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1679,8 +1807,20 @@
       <c r="AG1" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="AH1" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI1" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ1" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK1" s="28" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:37" ht="12.75">
       <c r="A2" s="6" t="s">
         <v>29</v>
       </c>
@@ -1724,8 +1864,12 @@
       <c r="AE2" s="6"/>
       <c r="AF2" s="6"/>
       <c r="AG2" s="10"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:37" ht="25.5">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
@@ -1773,8 +1917,12 @@
       <c r="AE3" s="6"/>
       <c r="AF3" s="6"/>
       <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:37" ht="12.75">
       <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
@@ -1814,8 +1962,12 @@
       <c r="AE4" s="6"/>
       <c r="AF4" s="6"/>
       <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="10"/>
+      <c r="AK4" s="10"/>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:37" ht="12.75">
       <c r="A5" s="6" t="s">
         <v>40</v>
       </c>
@@ -1889,8 +2041,20 @@
         <v>55</v>
       </c>
       <c r="AG5" s="10"/>
+      <c r="AH5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI5" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK5" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:37" ht="12.75">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
@@ -1932,8 +2096,12 @@
       <c r="AE6" s="6"/>
       <c r="AF6" s="6"/>
       <c r="AG6" s="10"/>
+      <c r="AH6" s="10"/>
+      <c r="AI6" s="10"/>
+      <c r="AJ6" s="10"/>
+      <c r="AK6" s="10"/>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:37" ht="12.75">
       <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
@@ -1973,8 +2141,12 @@
       <c r="AE7" s="6"/>
       <c r="AF7" s="6"/>
       <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="10"/>
+      <c r="AK7" s="10"/>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:37" ht="12.75">
       <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
@@ -2032,8 +2204,12 @@
       <c r="AG8" s="10" t="s">
         <v>81</v>
       </c>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="10"/>
+      <c r="AJ8" s="10"/>
+      <c r="AK8" s="10"/>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:37" ht="12.75">
       <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
@@ -2075,8 +2251,12 @@
       <c r="AE9" s="6"/>
       <c r="AF9" s="6"/>
       <c r="AG9" s="10"/>
+      <c r="AH9" s="10"/>
+      <c r="AI9" s="10"/>
+      <c r="AJ9" s="10"/>
+      <c r="AK9" s="10"/>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:37" ht="12.75">
       <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
@@ -2118,8 +2298,12 @@
       <c r="AE10" s="6"/>
       <c r="AF10" s="6"/>
       <c r="AG10" s="10"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="10"/>
+      <c r="AK10" s="10"/>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:37" ht="12.75">
       <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
@@ -2163,8 +2347,12 @@
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
       <c r="AG11" s="10"/>
+      <c r="AH11" s="10"/>
+      <c r="AI11" s="10"/>
+      <c r="AJ11" s="10"/>
+      <c r="AK11" s="10"/>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:37" ht="12.75">
       <c r="A12" s="18" t="s">
         <v>29</v>
       </c>
@@ -2208,8 +2396,12 @@
       <c r="AE12" s="6"/>
       <c r="AF12" s="6"/>
       <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
+      <c r="AK12" s="10"/>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:37" ht="12.75">
       <c r="A13" s="18" t="s">
         <v>34</v>
       </c>
@@ -2253,8 +2445,12 @@
       <c r="AE13" s="6"/>
       <c r="AF13" s="6"/>
       <c r="AG13" s="10"/>
+      <c r="AH13" s="10"/>
+      <c r="AI13" s="10"/>
+      <c r="AJ13" s="10"/>
+      <c r="AK13" s="10"/>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:37" ht="12.75">
       <c r="A14" s="18" t="s">
         <v>40</v>
       </c>
@@ -2302,6 +2498,10 @@
       <c r="AG14" s="10" t="s">
         <v>81</v>
       </c>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="2">
